--- a/기획/아이템 목록.xlsx
+++ b/기획/아이템 목록.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\typar\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\typar\OneDrive\바탕 화면\storage\기획\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CD9BE15-B8E3-4478-8BDD-081099AAE096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EAF8DFA-A3E7-4487-90CA-7D0DAB78673B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1250" yWindow="320" windowWidth="20700" windowHeight="19890" xr2:uid="{90E8086F-2B13-4029-8E7E-9F739A15DEF1}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{90E8086F-2B13-4029-8E7E-9F739A15DEF1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="아이템" sheetId="1" r:id="rId1"/>
+    <sheet name="퍽" sheetId="2" r:id="rId2"/>
+    <sheet name="업그레이드 트리" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="90">
   <si>
     <t>돈까스 김밥</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -167,6 +169,231 @@
   </si>
   <si>
     <t>아군 전체 화상 제거, 적에게 적용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅 획득 경험치 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅 방어 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전사 저항 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>레인저 명중 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>코인 획득량 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>힐러 회복량 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>슬롯 추가 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>슬롯 추가 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>높은 레벨 영웅 출현 확률 10%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>높은 레벨 영웅 출현 확률 15%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>높은 레벨 영웅 출현 확률 20%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>높은 레벨 영웅 출현 확률 25%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>특수 버프 부여 확률 5%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>특수 버프 부여 확률 10%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>특수 버프 부여 확률 15%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>의무실</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>회복량 +5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>회복량 +10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>회복량 +15</t>
+  </si>
+  <si>
+    <t>회복량 +20</t>
+  </si>
+  <si>
+    <t>회복 이후 특수 버프 부여 확률 10%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>회복 이후 특수 버프 부여 확률 15%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>회복 이후 특수 버프 부여 확률 20%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전체 슬롯 새로고침</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>알약 구매</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>알약 가격 감소 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>알약 가격 감소 2</t>
+  </si>
+  <si>
+    <t>네잎클로버</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>행운 부여</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사망 시 최대 체력의 30%로 부활</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>추적자 반지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 사용 대상에 표식 부여</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>슬라임 젤리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 사용 대상에 중독 부여</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무균 마카롱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아군 전체 디버프 제거</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방사선 캔디</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>적 전체 중독 부여</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매크로 주스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 행동 2회 반복</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레드보드 초콜릿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무작위 능력치 2개 버프</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>드론 모터 오일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자신 속도 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>관객 유도 선글라스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전투 시 적의 첫 공격 유도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>바람막이 도복</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>응급 혈액팩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>임상병리학과</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>태권도학과</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KPOP 학과</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전자공학과</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소프트웨어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방사선학과</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>간호학과</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사이버드론</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -213,9 +440,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -551,22 +781,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2E4E3B7-62A4-4077-9EE6-0ABECC8E5B48}">
-  <dimension ref="F4:N15"/>
+  <dimension ref="A4:N20"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="4" spans="6:14" x14ac:dyDescent="0.45">
-      <c r="F4" t="s">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="C4" t="s">
         <v>2</v>
       </c>
       <c r="L4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="6:14" x14ac:dyDescent="0.45">
-      <c r="F6" t="s">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="C6" t="s">
         <v>0</v>
       </c>
-      <c r="H6" t="s">
+      <c r="E6" t="s">
         <v>25</v>
       </c>
       <c r="L6" t="s">
@@ -576,11 +806,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="6:14" x14ac:dyDescent="0.45">
-      <c r="F7" t="s">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="C7" t="s">
         <v>1</v>
       </c>
-      <c r="H7" t="s">
+      <c r="E7" t="s">
         <v>26</v>
       </c>
       <c r="L7" t="s">
@@ -590,11 +820,11 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="6:14" x14ac:dyDescent="0.45">
-      <c r="F8" t="s">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="C8" t="s">
         <v>4</v>
       </c>
-      <c r="H8" t="s">
+      <c r="E8" t="s">
         <v>27</v>
       </c>
       <c r="L8" t="s">
@@ -604,11 +834,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="6:14" x14ac:dyDescent="0.45">
-      <c r="F9" t="s">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="C9" t="s">
         <v>5</v>
       </c>
-      <c r="H9" t="s">
+      <c r="E9" t="s">
         <v>6</v>
       </c>
       <c r="L9" t="s">
@@ -618,11 +848,11 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="6:14" x14ac:dyDescent="0.45">
-      <c r="F10" t="s">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="C10" t="s">
         <v>21</v>
       </c>
-      <c r="H10" t="s">
+      <c r="E10" t="s">
         <v>22</v>
       </c>
       <c r="L10" t="s">
@@ -632,11 +862,11 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="6:14" x14ac:dyDescent="0.45">
-      <c r="F11" t="s">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="C11" t="s">
         <v>23</v>
       </c>
-      <c r="H11" t="s">
+      <c r="E11" t="s">
         <v>20</v>
       </c>
       <c r="L11" t="s">
@@ -646,11 +876,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="6:14" x14ac:dyDescent="0.45">
-      <c r="F12" t="s">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="C12" t="s">
         <v>24</v>
       </c>
-      <c r="H12" t="s">
+      <c r="E12" t="s">
         <v>30</v>
       </c>
       <c r="L12" t="s">
@@ -660,24 +890,427 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="6:14" x14ac:dyDescent="0.45">
-      <c r="F13" t="s">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="C13" t="s">
         <v>28</v>
       </c>
-      <c r="H13" t="s">
+      <c r="E13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="6:14" x14ac:dyDescent="0.45">
-      <c r="F15" t="s">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="C14" t="s">
         <v>31</v>
       </c>
-      <c r="H15" t="s">
+      <c r="E14" t="s">
         <v>32</v>
+      </c>
+      <c r="L14" t="s">
+        <v>61</v>
+      </c>
+      <c r="N14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="J15" t="s">
+        <v>82</v>
+      </c>
+      <c r="L15" t="s">
+        <v>81</v>
+      </c>
+      <c r="N15" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" t="s">
+        <v>68</v>
+      </c>
+      <c r="E16" t="s">
+        <v>69</v>
+      </c>
+      <c r="L16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N16" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" t="s">
+        <v>70</v>
+      </c>
+      <c r="E17" t="s">
+        <v>71</v>
+      </c>
+      <c r="L17" t="s">
+        <v>66</v>
+      </c>
+      <c r="N17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" t="s">
+        <v>72</v>
+      </c>
+      <c r="E18" t="s">
+        <v>73</v>
+      </c>
+      <c r="J18" t="s">
+        <v>84</v>
+      </c>
+      <c r="L18" t="s">
+        <v>78</v>
+      </c>
+      <c r="N18" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>85</v>
+      </c>
+      <c r="C19" t="s">
+        <v>74</v>
+      </c>
+      <c r="E19" t="s">
+        <v>75</v>
+      </c>
+      <c r="J19" t="s">
+        <v>83</v>
+      </c>
+      <c r="L19" t="s">
+        <v>80</v>
+      </c>
+      <c r="N19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>89</v>
+      </c>
+      <c r="C20" t="s">
+        <v>76</v>
+      </c>
+      <c r="E20" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4453590E-670E-411D-8D99-7A466A0FF7A4}">
+  <dimension ref="B3:B8"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9FEF0C6-B538-42E0-A933-8FB96F648096}">
+  <dimension ref="C4:M21"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="4" spans="3:13" x14ac:dyDescent="0.45">
+      <c r="C4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+    </row>
+    <row r="5" spans="3:13" x14ac:dyDescent="0.45">
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+    </row>
+    <row r="6" spans="3:13" x14ac:dyDescent="0.45">
+      <c r="C6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" spans="3:13" x14ac:dyDescent="0.45">
+      <c r="C7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="3:13" x14ac:dyDescent="0.45">
+      <c r="C8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="3:13" x14ac:dyDescent="0.45">
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" spans="3:13" x14ac:dyDescent="0.45">
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+    </row>
+    <row r="15" spans="3:13" x14ac:dyDescent="0.45">
+      <c r="C15" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+    </row>
+    <row r="16" spans="3:13" x14ac:dyDescent="0.45">
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.45">
+      <c r="C17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="M17" s="1"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.45">
+      <c r="C18" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="M18" s="1"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.45">
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="M19" s="1"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.45">
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.45">
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="35">
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="H20:K20"/>
+    <mergeCell ref="H21:K21"/>
+    <mergeCell ref="C15:M16"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="H17:K17"/>
+    <mergeCell ref="H18:K18"/>
+    <mergeCell ref="H19:K19"/>
+    <mergeCell ref="C4:K5"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/기획/아이템 목록.xlsx
+++ b/기획/아이템 목록.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\typar\OneDrive\바탕 화면\storage\기획\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\typar\Desktop\storage\기획\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EAF8DFA-A3E7-4487-90CA-7D0DAB78673B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19AF3259-1BA4-4830-94AE-688CF21A4C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{90E8086F-2B13-4029-8E7E-9F739A15DEF1}"/>
+    <workbookView xWindow="-18377" yWindow="-3849" windowWidth="18240" windowHeight="15952" xr2:uid="{90E8086F-2B13-4029-8E7E-9F739A15DEF1}"/>
   </bookViews>
   <sheets>
     <sheet name="아이템" sheetId="1" r:id="rId1"/>
@@ -781,230 +781,230 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2E4E3B7-62A4-4077-9EE6-0ABECC8E5B48}">
-  <dimension ref="A4:N20"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <dimension ref="B4:O20"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="C4" t="s">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="D4" t="s">
         <v>2</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="C6" t="s">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="D6" t="s">
         <v>0</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>25</v>
       </c>
-      <c r="L6" t="s">
+      <c r="M6" t="s">
         <v>7</v>
       </c>
-      <c r="N6" t="s">
+      <c r="O6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="C7" t="s">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="D7" t="s">
         <v>1</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>26</v>
       </c>
-      <c r="L7" t="s">
+      <c r="M7" t="s">
         <v>8</v>
       </c>
-      <c r="N7" t="s">
+      <c r="O7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="C8" t="s">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="D8" t="s">
         <v>4</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>27</v>
       </c>
-      <c r="L8" t="s">
+      <c r="M8" t="s">
         <v>9</v>
       </c>
-      <c r="N8" t="s">
+      <c r="O8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="C9" t="s">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="D9" t="s">
         <v>5</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>6</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>13</v>
       </c>
-      <c r="N9" t="s">
+      <c r="O9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="C10" t="s">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="D10" t="s">
         <v>21</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>22</v>
       </c>
-      <c r="L10" t="s">
+      <c r="M10" t="s">
         <v>15</v>
       </c>
-      <c r="N10" t="s">
+      <c r="O10" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="C11" t="s">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="D11" t="s">
         <v>23</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>20</v>
       </c>
-      <c r="L11" t="s">
+      <c r="M11" t="s">
         <v>17</v>
       </c>
-      <c r="N11" t="s">
+      <c r="O11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="C12" t="s">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="D12" t="s">
         <v>24</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>30</v>
       </c>
-      <c r="L12" t="s">
+      <c r="M12" t="s">
         <v>18</v>
       </c>
-      <c r="N12" t="s">
+      <c r="O12" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="C13" t="s">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="D13" t="s">
         <v>28</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="C14" t="s">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="D14" t="s">
         <v>31</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>32</v>
       </c>
-      <c r="L14" t="s">
+      <c r="M14" t="s">
         <v>61</v>
       </c>
-      <c r="N14" t="s">
+      <c r="O14" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="J15" t="s">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K15" t="s">
         <v>82</v>
       </c>
-      <c r="L15" t="s">
+      <c r="M15" t="s">
         <v>81</v>
       </c>
-      <c r="N15" t="s">
+      <c r="O15" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
         <v>88</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>68</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>69</v>
       </c>
-      <c r="L16" t="s">
+      <c r="M16" t="s">
         <v>64</v>
       </c>
-      <c r="N16" t="s">
+      <c r="O16" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
         <v>87</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>70</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>71</v>
       </c>
-      <c r="L17" t="s">
+      <c r="M17" t="s">
         <v>66</v>
       </c>
-      <c r="N17" t="s">
+      <c r="O17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
         <v>86</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>72</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>73</v>
       </c>
-      <c r="J18" t="s">
+      <c r="K18" t="s">
         <v>84</v>
       </c>
-      <c r="L18" t="s">
+      <c r="M18" t="s">
         <v>78</v>
       </c>
-      <c r="N18" t="s">
+      <c r="O18" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
         <v>85</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>74</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>75</v>
       </c>
-      <c r="J19" t="s">
+      <c r="K19" t="s">
         <v>83</v>
       </c>
-      <c r="L19" t="s">
+      <c r="M19" t="s">
         <v>80</v>
       </c>
-      <c r="N19" t="s">
+      <c r="O19" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
         <v>89</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>76</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1017,34 +1017,34 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4453590E-670E-411D-8D99-7A466A0FF7A4}">
   <dimension ref="B3:B8"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>38</v>
       </c>
@@ -1058,9 +1058,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9FEF0C6-B538-42E0-A933-8FB96F648096}">
   <dimension ref="C4:M21"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="4" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="4" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C4" s="1" t="s">
         <v>39</v>
       </c>
@@ -1073,7 +1073,7 @@
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
     </row>
-    <row r="5" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="5" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
@@ -1084,7 +1084,7 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
     </row>
-    <row r="6" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="6" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C6" s="1" t="s">
         <v>40</v>
       </c>
@@ -1101,7 +1101,7 @@
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
     </row>
-    <row r="7" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="7" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C7" s="1" t="s">
         <v>41</v>
       </c>
@@ -1118,7 +1118,7 @@
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
     </row>
-    <row r="8" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="8" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C8" s="1" t="s">
         <v>57</v>
       </c>
@@ -1135,7 +1135,7 @@
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
     </row>
-    <row r="9" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="9" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1" t="s">
@@ -1148,7 +1148,7 @@
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
     </row>
-    <row r="10" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="10" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -1159,7 +1159,7 @@
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
     </row>
-    <row r="15" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="15" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C15" s="1" t="s">
         <v>49</v>
       </c>
@@ -1174,7 +1174,7 @@
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
     </row>
-    <row r="16" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="16" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -1187,7 +1187,7 @@
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
     </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C17" s="1" t="s">
         <v>40</v>
       </c>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="M17" s="1"/>
     </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C18" s="1" t="s">
         <v>41</v>
       </c>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M18" s="1"/>
     </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1" t="s">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="M19" s="1"/>
     </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
@@ -1261,7 +1261,7 @@
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
     </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
@@ -1274,6 +1274,25 @@
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="C4:K5"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
     <mergeCell ref="I9:K9"/>
     <mergeCell ref="I10:K10"/>
     <mergeCell ref="H20:K20"/>
@@ -1285,30 +1304,11 @@
     <mergeCell ref="H17:K17"/>
     <mergeCell ref="H18:K18"/>
     <mergeCell ref="H19:K19"/>
-    <mergeCell ref="C4:K5"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="E7:H7"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="E20:G20"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="E21:G21"/>
-    <mergeCell ref="E8:H8"/>
     <mergeCell ref="E9:H9"/>
-    <mergeCell ref="E10:H10"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:G19"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/기획/아이템 목록.xlsx
+++ b/기획/아이템 목록.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\typar\Desktop\storage\기획\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\typar\OneDrive\바탕 화면\storage\기획\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19AF3259-1BA4-4830-94AE-688CF21A4C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8659451-5E06-4C4C-8F56-AF69E5D563A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-18377" yWindow="-3849" windowWidth="18240" windowHeight="15952" xr2:uid="{90E8086F-2B13-4029-8E7E-9F739A15DEF1}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{90E8086F-2B13-4029-8E7E-9F739A15DEF1}"/>
   </bookViews>
   <sheets>
     <sheet name="아이템" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="93">
   <si>
     <t>돈까스 김밥</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -270,10 +270,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>알약 구매</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>알약 가격 감소 1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -394,6 +390,22 @@
   </si>
   <si>
     <t>사이버드론</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>알약 구매 가능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 영웅 수 +3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 영웅 수 +6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 영웅 수 +9</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -781,10 +793,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2E4E3B7-62A4-4077-9EE6-0ABECC8E5B48}">
-  <dimension ref="B4:O20"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="B4:O21"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.45">
       <c r="D4" t="s">
         <v>2</v>
       </c>
@@ -792,7 +804,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.45">
       <c r="D6" t="s">
         <v>0</v>
       </c>
@@ -806,7 +818,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.45">
       <c r="D7" t="s">
         <v>1</v>
       </c>
@@ -820,7 +832,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.45">
       <c r="D8" t="s">
         <v>4</v>
       </c>
@@ -834,7 +846,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.45">
       <c r="D9" t="s">
         <v>5</v>
       </c>
@@ -848,7 +860,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.45">
       <c r="D10" t="s">
         <v>21</v>
       </c>
@@ -862,7 +874,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.45">
       <c r="D11" t="s">
         <v>23</v>
       </c>
@@ -876,7 +888,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.45">
       <c r="D12" t="s">
         <v>24</v>
       </c>
@@ -890,7 +902,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.45">
       <c r="D13" t="s">
         <v>28</v>
       </c>
@@ -898,114 +910,114 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.45">
       <c r="D14" t="s">
         <v>31</v>
       </c>
       <c r="F14" t="s">
         <v>32</v>
       </c>
-      <c r="M14" t="s">
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B16" t="s">
+        <v>87</v>
+      </c>
+      <c r="D16" t="s">
+        <v>67</v>
+      </c>
+      <c r="F16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M16" t="s">
+        <v>60</v>
+      </c>
+      <c r="O16" t="s">
         <v>61</v>
       </c>
-      <c r="O14" t="s">
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B17" t="s">
+        <v>86</v>
+      </c>
+      <c r="D17" t="s">
+        <v>69</v>
+      </c>
+      <c r="F17" t="s">
+        <v>70</v>
+      </c>
+      <c r="K17" t="s">
+        <v>81</v>
+      </c>
+      <c r="M17" t="s">
+        <v>80</v>
+      </c>
+      <c r="O17" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="K15" t="s">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B18" t="s">
+        <v>85</v>
+      </c>
+      <c r="D18" t="s">
+        <v>71</v>
+      </c>
+      <c r="F18" t="s">
+        <v>72</v>
+      </c>
+      <c r="M18" t="s">
+        <v>63</v>
+      </c>
+      <c r="O18" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B19" t="s">
+        <v>84</v>
+      </c>
+      <c r="D19" t="s">
+        <v>73</v>
+      </c>
+      <c r="F19" t="s">
+        <v>74</v>
+      </c>
+      <c r="M19" t="s">
+        <v>65</v>
+      </c>
+      <c r="O19" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D20" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" t="s">
+        <v>76</v>
+      </c>
+      <c r="K20" t="s">
+        <v>83</v>
+      </c>
+      <c r="M20" t="s">
+        <v>77</v>
+      </c>
+      <c r="O20" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="K21" t="s">
         <v>82</v>
       </c>
-      <c r="M15" t="s">
-        <v>81</v>
-      </c>
-      <c r="O15" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B16" t="s">
-        <v>88</v>
-      </c>
-      <c r="D16" t="s">
-        <v>68</v>
-      </c>
-      <c r="F16" t="s">
-        <v>69</v>
-      </c>
-      <c r="M16" t="s">
-        <v>64</v>
-      </c>
-      <c r="O16" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B17" t="s">
-        <v>87</v>
-      </c>
-      <c r="D17" t="s">
-        <v>70</v>
-      </c>
-      <c r="F17" t="s">
-        <v>71</v>
-      </c>
-      <c r="M17" t="s">
-        <v>66</v>
-      </c>
-      <c r="O17" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B18" t="s">
-        <v>86</v>
-      </c>
-      <c r="D18" t="s">
-        <v>72</v>
-      </c>
-      <c r="F18" t="s">
-        <v>73</v>
-      </c>
-      <c r="K18" t="s">
-        <v>84</v>
-      </c>
-      <c r="M18" t="s">
-        <v>78</v>
-      </c>
-      <c r="O18" t="s">
+      <c r="M21" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B19" t="s">
-        <v>85</v>
-      </c>
-      <c r="D19" t="s">
-        <v>74</v>
-      </c>
-      <c r="F19" t="s">
-        <v>75</v>
-      </c>
-      <c r="K19" t="s">
-        <v>83</v>
-      </c>
-      <c r="M19" t="s">
-        <v>80</v>
-      </c>
-      <c r="O19" t="s">
+      <c r="O21" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B20" t="s">
-        <v>89</v>
-      </c>
-      <c r="D20" t="s">
-        <v>76</v>
-      </c>
-      <c r="F20" t="s">
-        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1017,34 +1029,34 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4453590E-670E-411D-8D99-7A466A0FF7A4}">
   <dimension ref="B3:B8"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>38</v>
       </c>
@@ -1058,9 +1070,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9FEF0C6-B538-42E0-A933-8FB96F648096}">
   <dimension ref="C4:M21"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="4" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C4" s="1" t="s">
         <v>39</v>
       </c>
@@ -1072,8 +1084,10 @@
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
-    </row>
-    <row r="5" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
@@ -1083,8 +1097,10 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
-    </row>
-    <row r="6" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+    </row>
+    <row r="6" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C6" s="1" t="s">
         <v>40</v>
       </c>
@@ -1100,8 +1116,12 @@
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
-    </row>
-    <row r="7" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="L6" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="M6" s="1"/>
+    </row>
+    <row r="7" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C7" s="1" t="s">
         <v>41</v>
       </c>
@@ -1117,8 +1137,12 @@
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
-    </row>
-    <row r="8" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="L7" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="M7" s="1"/>
+    </row>
+    <row r="8" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C8" s="1" t="s">
         <v>57</v>
       </c>
@@ -1134,8 +1158,12 @@
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
-    </row>
-    <row r="9" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="L8" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="M8" s="1"/>
+    </row>
+    <row r="9" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1" t="s">
@@ -1148,7 +1176,7 @@
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
     </row>
-    <row r="10" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -1159,7 +1187,7 @@
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
     </row>
-    <row r="15" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C15" s="1" t="s">
         <v>49</v>
       </c>
@@ -1174,7 +1202,7 @@
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
     </row>
-    <row r="16" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -1187,7 +1215,7 @@
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
     </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C17" s="1" t="s">
         <v>40</v>
       </c>
@@ -1204,11 +1232,11 @@
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="M17" s="1"/>
     </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C18" s="1" t="s">
         <v>41</v>
       </c>
@@ -1225,11 +1253,11 @@
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M18" s="1"/>
     </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1" t="s">
@@ -1244,11 +1272,11 @@
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M19" s="1"/>
     </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
@@ -1261,7 +1289,7 @@
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
     </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
@@ -1273,7 +1301,11 @@
       <c r="K21" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="35">
+  <mergeCells count="38">
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="C4:M5"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="E19:G19"/>
     <mergeCell ref="C8:D8"/>
@@ -1284,7 +1316,6 @@
     <mergeCell ref="E17:G17"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="E18:G18"/>
-    <mergeCell ref="C4:K5"/>
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="I7:K7"/>
     <mergeCell ref="I8:K8"/>

--- a/기획/아이템 목록.xlsx
+++ b/기획/아이템 목록.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\typar\OneDrive\바탕 화면\storage\기획\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\typar\Desktop\storage\기획\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8659451-5E06-4C4C-8F56-AF69E5D563A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{880A0059-94D3-4EFB-954B-F1C8D69FDF53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{90E8086F-2B13-4029-8E7E-9F739A15DEF1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{90E8086F-2B13-4029-8E7E-9F739A15DEF1}"/>
   </bookViews>
   <sheets>
     <sheet name="아이템" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="94">
   <si>
     <t>돈까스 김밥</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -406,6 +406,10 @@
   </si>
   <si>
     <t>최대 영웅 수 +9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>회복 시간 감소</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -794,9 +798,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2E4E3B7-62A4-4077-9EE6-0ABECC8E5B48}">
   <dimension ref="B4:O21"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D4" t="s">
         <v>2</v>
       </c>
@@ -804,7 +808,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
         <v>0</v>
       </c>
@@ -818,7 +822,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
         <v>1</v>
       </c>
@@ -832,7 +836,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
         <v>4</v>
       </c>
@@ -846,7 +850,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D9" t="s">
         <v>5</v>
       </c>
@@ -860,7 +864,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
         <v>21</v>
       </c>
@@ -874,7 +878,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D11" t="s">
         <v>23</v>
       </c>
@@ -888,7 +892,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
         <v>24</v>
       </c>
@@ -902,7 +906,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D13" t="s">
         <v>28</v>
       </c>
@@ -910,7 +914,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D14" t="s">
         <v>31</v>
       </c>
@@ -918,7 +922,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>87</v>
       </c>
@@ -935,7 +939,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>86</v>
       </c>
@@ -955,7 +959,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>85</v>
       </c>
@@ -972,7 +976,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>84</v>
       </c>
@@ -989,7 +993,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>88</v>
       </c>
@@ -1009,7 +1013,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K21" t="s">
         <v>82</v>
       </c>
@@ -1029,34 +1033,34 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4453590E-670E-411D-8D99-7A466A0FF7A4}">
   <dimension ref="B3:B8"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>38</v>
       </c>
@@ -1069,10 +1073,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9FEF0C6-B538-42E0-A933-8FB96F648096}">
-  <dimension ref="C4:M21"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <dimension ref="C4:O21"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="4" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="4" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C4" s="1" t="s">
         <v>39</v>
       </c>
@@ -1087,7 +1091,7 @@
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
     </row>
-    <row r="5" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="5" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
@@ -1100,7 +1104,7 @@
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
     </row>
-    <row r="6" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="6" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C6" s="1" t="s">
         <v>40</v>
       </c>
@@ -1121,7 +1125,7 @@
       </c>
       <c r="M6" s="1"/>
     </row>
-    <row r="7" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="7" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C7" s="1" t="s">
         <v>41</v>
       </c>
@@ -1142,7 +1146,7 @@
       </c>
       <c r="M7" s="1"/>
     </row>
-    <row r="8" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="8" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C8" s="1" t="s">
         <v>57</v>
       </c>
@@ -1163,7 +1167,7 @@
       </c>
       <c r="M8" s="1"/>
     </row>
-    <row r="9" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="9" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1" t="s">
@@ -1176,7 +1180,7 @@
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
     </row>
-    <row r="10" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="10" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -1187,7 +1191,7 @@
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
     </row>
-    <row r="15" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="15" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C15" s="1" t="s">
         <v>49</v>
       </c>
@@ -1201,8 +1205,10 @@
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
-    </row>
-    <row r="16" spans="3:13" x14ac:dyDescent="0.45">
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+    </row>
+    <row r="16" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -1214,8 +1220,10 @@
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.45">
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C17" s="1" t="s">
         <v>40</v>
       </c>
@@ -1235,8 +1243,12 @@
         <v>89</v>
       </c>
       <c r="M17" s="1"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.45">
+      <c r="N17" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="O17" s="1"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C18" s="1" t="s">
         <v>41</v>
       </c>
@@ -1256,8 +1268,12 @@
         <v>58</v>
       </c>
       <c r="M18" s="1"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.45">
+      <c r="N18" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="O18" s="1"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1" t="s">
@@ -1276,7 +1292,7 @@
       </c>
       <c r="M19" s="1"/>
     </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
@@ -1289,7 +1305,7 @@
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
     </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
@@ -1301,7 +1317,31 @@
       <c r="K21" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="38">
+  <mergeCells count="40">
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="C15:O16"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="H20:K20"/>
+    <mergeCell ref="H21:K21"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="H17:K17"/>
+    <mergeCell ref="H18:K18"/>
+    <mergeCell ref="H19:K19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
     <mergeCell ref="L6:M6"/>
     <mergeCell ref="L7:M7"/>
     <mergeCell ref="L8:M8"/>
@@ -1318,28 +1358,6 @@
     <mergeCell ref="E18:G18"/>
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="I7:K7"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="H20:K20"/>
-    <mergeCell ref="H21:K21"/>
-    <mergeCell ref="C15:M16"/>
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="H17:K17"/>
-    <mergeCell ref="H18:K18"/>
-    <mergeCell ref="H19:K19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:G20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:G21"/>
-    <mergeCell ref="E9:H9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
